--- a/R Markdown/resultados/Produtos_Cesta_2026/tabelas/top10_acoes_cesta_por_subprefeitura.xlsx
+++ b/R Markdown/resultados/Produtos_Cesta_2026/tabelas/top10_acoes_cesta_por_subprefeitura.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/resultados/Produtos_Cesta_2026/tabelas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_23C7E0C387F2F72DBD9F3E52D65E7FECE45A39E2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25A5D553-8D9D-4118-823C-E499DA7E11C2}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_23C7E0C387F2F72DBD9F3E52D65E7FECE45A39E2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9D57C34-C601-4B6C-83A5-9A88D4992162}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="subprefeitura_aricanduva_for..." sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3477" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3476" uniqueCount="827">
   <si>
     <t>Código</t>
   </si>
@@ -2908,8 +2908,8 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
+      <c r="A2">
+        <v>1170</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
